--- a/data/activity_log.xlsx
+++ b/data/activity_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2606,6 +2606,831 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-03 12:46:10</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>__solo__</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>pin=114951 quiz=citi-trivia bots=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-03 12:46:10</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>QuizNinja</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>pin=114951 players=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-03 12:46:19</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>QuizNinja</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>q=1 correct=True points=1616</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-03 12:46:25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>QuizNinja</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-03 12:46:27</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>QuizNinja</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>q=3 correct=True points=2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-03 12:46:30</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>QuizNinja</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>q=4 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-03 12:59:45</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>__solo__</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>pin=756224 quiz=citi-trivia bots=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-03 12:59:45</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>QuizNinja</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>pin=756224 players=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:00:42</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>__solo__</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>pin=756224</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:01:07</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>__solo__</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>pin=111397 quiz=citi-trivia bots=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:01:07</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>QuizNinja</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>pin=111397 players=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:01:18</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>__solo__</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>pin=111397</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:02:09</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:03:55</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:04:18</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>pin=317872 quiz=bank-260703-105649 bots=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:04:54</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>pin=317872 players=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:05:21</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>pin=317872</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:06:37</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin@citi.com </t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:07:12</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>pin=721252 quiz=bank-260703-105649 bots=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:07:24</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>pin=721252 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:07:38</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>pin=721252 players=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:07:54</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:08:16</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>q=2 correct=True points=1627</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:08:46</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>q=3 correct=True points=1601</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:09:42</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>q=5 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:10:16</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>subjective_answer</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>q=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:10:22</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>vote_cast</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>for=NightOwl_Sam q=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:10:56</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>force_reveal</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>q=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:11:01</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>force_reveal</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>q=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:11:04</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>force_reveal</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>q=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:11:20</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>pin=721252</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/activity_log.xlsx
+++ b/data/activity_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3431,6 +3431,6658 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:39:58</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>__solo__</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>pin=988288 quiz=citi-trivia bots=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:39:58</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>QuizNinja</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>pin=988288 players=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:40:06</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>QuizNinja</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:54:52</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:55:06</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>pin=988288</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:59:23</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:00:39</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>pin=824971 quiz=bank-260702-225447 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:01:27</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>quiz_built_from_bank</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>bank-260703-140125 n=10 subj=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:01:44</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>pin=838359 quiz=bank-260703-105649 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:02:21</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:02:26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>pin=162926 quiz=bank-260703-140125 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:02:35</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Rajat Gupta</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>pin=162926 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:03:04</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>pin=162926 players=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:03:20</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Rajat Gupta</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>subjective_answer</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>q=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:04:02</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>pin=162926</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:04:40</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>quiz_built_from_bank</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>bank-260703-140439 n=10 subj=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:10:25</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>login_failed</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:10:36</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:11:02</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>pin=526889 quiz=bank-260703-140439 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:11:14</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>pin=526889 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:11:31</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>pin=526889 players=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:11:37</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>subjective_answer</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>q=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:11:47</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>force_end_voting</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>q=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:11:50</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>pin=526889</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:12:03</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:13:05</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>quiz_built_from_bank</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>bank-260703-141304 n=5 subj=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:13:30</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>pin=354694 quiz=bank-260703-141304 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:13:49</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>pLAYER1</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>pin=354694 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:14:09</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>pLAYER2</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>pin=354694 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:14:33</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>pin=354694 players=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:14:46</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>pLAYER1</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:14:51</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>pLAYER2</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>q=1 correct=True points=1151</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:15:24</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>pLAYER1</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>subjective_answer</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>q=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:15:28</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>pLAYER2</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>subjective_answer</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>q=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:15:32</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>pLAYER2</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>vote_cast</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>for=pLAYER1 q=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:15:35</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>pLAYER1</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>vote_cast</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>for=pLAYER2 q=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:15:48</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>pLAYER1</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>q=3 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:15:53</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>pLAYER2</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>q=3 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:16:02</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>pLAYER1</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>q=4 correct=True points=1803</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:16:04</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>pLAYER2</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>q=4 correct=True points=1699</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:16:37</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>pLAYER1</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>q=5 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:16:39</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>pLAYER2</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>q=5 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:16:51</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>pin=354694</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:30:45</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>quiz_built_from_bank</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>bank-260703-143043 n=10 subj=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:11:02</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:19:59</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:21:08</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>pin=221887 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:21:28</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Rajat Gupta</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>pin=221887 soeid=RG22983 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:25:56</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>pin=221887 soeid=RG22985 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:41:32</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin@citi.com </t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:41:55</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>pin=148564 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:42:22</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>pin=148564 soeid=RG22983 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:43:13</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>pin=148564 soeid=AB12345 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:43:28</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>pin=148564 players=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:43:39</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:43:42</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:44:04</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:44:07</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:44:20</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>q=3 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:44:22</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>q=3 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:44:39</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>q=4 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:44:43</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>q=4 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:48:38</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>pin=148564</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:48:55</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>pin=244467 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:49:24</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Hulk_The_Hacker</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>pin=244467 soeid=RG22983 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:49:55</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>pin=244467 players=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:50:02</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Hulk_The_Hacker</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:54:12</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>pin=244467</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:54:22</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>pin=272396 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:54:31</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>pin=272396 soeid=TT12345 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:54:55</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>pin=272396 players=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:55:19</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:59:41</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:59:46</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>pin=488374 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:59:56</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>pin=863578 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:00:12</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>pin=863578 soeid=AB12345 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:00:29</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>pin=863578 players=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:00:48</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>q=1 correct=True points=1414</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:00:56</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:01:05</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>q=3 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:01:30</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>q=4 correct=True points=1409</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:01:48</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>q=5 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:07:09</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:07:15</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>pin=863578</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:07:25</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>pin=868713 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:08:01</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>pin=868713 soeid=AB12345 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:08:09</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>pin=868713 players=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:08:18</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:08:42</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:11:03</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin@citi.com </t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:11:11</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>pin=868713</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:11:21</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>pin=244293 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:12:15</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>pin=244293 soeid=AB12346 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:12:19</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>pin=244293 soeid=AB12345 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:12:36</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>pin=244293 players=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:12:40</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:12:48</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:13:12</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:16:07</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:16:11</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>force_reveal</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>q=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:16:13</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>pin=244293</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:16:25</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>pin=135848 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:16:42</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>pin=135848 soeid=RG22983 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:16:54</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>pin=135848 soeid=AB12345 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:17:16</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>pin=135848 players=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:17:20</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:17:26</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:17:36</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:17:41</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:20:05</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin@citi.com </t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:20:10</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>pin=135848</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:20:19</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>pin=889341 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:20:40</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>pin=889341 soeid=AB12345 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:20:54</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>pin=889341 soeid=AB23456 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:21:09</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>pin=889341 players=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:21:25</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:21:29</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>q=1 correct=True points=1373</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:25:09</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>q=7 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:26:31</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin@citi.com </t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:26:36</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>pin=889341</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:26:44</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>pin=741432 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:26:53</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>pin=146379 quiz=bank-260703-141304 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:27:15</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>pin=146379 soeid=AB12345 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:27:29</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>pin=146379 soeid=AB23456 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:27:42</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>pin=146379 players=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:27:47</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:27:55</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:28:16</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>subjective_answer</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>q=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:28:24</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>subjective_answer</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>q=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:28:26</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>vote_cast</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>for=Rahul q=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:28:29</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>vote_cast</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>for=Player1 q=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:28:54</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>q=3 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:28:56</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>q=3 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:33:22</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:33:28</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>pin=146379</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:33:47</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>pin=915778 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:34:05</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>pin=915778 soeid=AB12345 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:34:19</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>pin=915778 soeid=AB23456 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:34:27</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>pin=915778 players=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:34:37</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>q=1 correct=True points=1724</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:34:41</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>q=1 correct=True points=1588</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:35:00</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:35:02</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:35:31</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>q=3 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:35:50</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>q=4 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:35:53</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>q=4 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:44:23</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:44:27</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>pin=915778</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:44:34</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>pin=253222 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:44:51</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>pin=253222 soeid=AB11111 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:45:27</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>pin=253222 soeid=AB22222 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:45:34</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>pin=253222 players=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:45:38</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:45:40</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>q=1 correct=True points=1873</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:47:13</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>q=4 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:47:26</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>q=4 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:47:37</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>q=5 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:47:50</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>q=5 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:48:07</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>q=6 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:48:09</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>q=6 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:48:32</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>q=7 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:48:35</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>q=7 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:50:06</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Player1</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>q=10 correct=True points=1807</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:50:09</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Player2</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>q=10 correct=True points=1673</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:58:22</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:58:28</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>pin=253222</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:58:44</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>pin=323743 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:59:01</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>pin=323743 soeid=AB11111 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:59:10</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>pin=323743 soeid=AB33445 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:59:32</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>pin=323743 players=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:59:36</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:59:40</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:59:53</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:59:55</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:00:12</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>q=3 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:00:13</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>q=3 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:00:40</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>q=4 correct=True points=1464</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:00:42</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>q=4 correct=True points=1380</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:02:02</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>q=7 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:02:09</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>q=7 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:10:35</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:10:41</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>pin=323743</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:11:40</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>pin=917529 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:11:53</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>pin=917529 soeid=AB11111 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:12:04</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>pin=917529 players=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:12:09</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>q=1 correct=True points=1859</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:12:25</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>q=2 correct=True points=1843</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:12:37</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>q=3 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:12:47</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>q=4 correct=True points=2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:12:58</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>q=5 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:13:07</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>q=6 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:13:18</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>q=7 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:13:29</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>q=8 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:13:39</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>q=9 correct=True points=1992</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:13:49</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>q=10 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:14:11</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>pin=917529</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:23:57</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:29:49</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">host@citi.com </t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>login_failed</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:29:58</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">host@citi.com </t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>login_failed</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:30:00</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">host@citi.com </t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>login_failed</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:30:01</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">host@citi.com </t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>login_failed</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:30:25</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>login_failed</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:30:27</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>login_failed</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:30:45</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>login_failed</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:30:56</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> admin@citi.com </t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>login_failed</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:32:39</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:33:38</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>pin=657259 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:33:51</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>pin=657259 soeid=RG22983 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:34:03</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>pin=657259 players=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:34:18</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>q=1 correct=True points=1553</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:34:29</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:34:40</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>q=3 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:35:18</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>q=4 correct=True points=1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:35:31</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>q=5 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:35:41</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>q=6 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:35:51</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>q=7 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:36:09</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>q=8 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:36:42</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>q=9 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:37:06</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Rajat</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>q=10 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:37:29</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>pin=657259</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:55:02</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:55:32</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:56:01</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:56:16</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr"/>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>login_failed</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:56:28</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:56:49</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>pin=628621 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:56:58</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>pin=628621 soeid=AB12345 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:57:16</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>pin=628621 players=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:57:19</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>q=1 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:57:35</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>q=2 correct=False points=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:58:05</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>force_reveal</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>q=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:58:09</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>pin=628621</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:01:50</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:15:28</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>login_ok</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:16:14</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>team_deleted</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Ops Avengers</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:16:21</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>team_deleted</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Blue Sparks</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:16:28</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>team_deleted</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:16:46</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>team_created</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Assistant Warrior</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:16:53</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>team_deleted</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Gold Rush</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:17:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>team_deleted</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Teal Titans</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:17:07</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>team_deleted</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>CX Crusaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:17:28</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>team_created</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>IVR Crusaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:17:51</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>pin=649167 quiz=bank-260703-143043 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:18:01</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>pin=649167 soeid=AB12345 team=-</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:18:22</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>game_started</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>pin=649167 players=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:18:26</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>q=1 correct=True points=1915</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:18:38</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>answer_submitted</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>q=2 correct=True points=2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:19:11</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>force_reveal</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>q=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:19:14</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>game_ended</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>pin=649167</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:19:36</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>pin=859534 quiz=bank-260703-141304 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:19:37</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>admin@citi.com</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>game_created</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>pin=974544 quiz=bank-260703-141304 bots=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:19:44</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>joined_game</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>pin=974544 soeid=AB12345 team=Assistant Warrior</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
